--- a/artfynd/A 18968-2023 artfynd.xlsx
+++ b/artfynd/A 18968-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18968-2023 artfynd.xlsx
+++ b/artfynd/A 18968-2023 artfynd.xlsx
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86361322</v>
+        <v>86361320</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>220785</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,31 +703,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gofarstorps gamla tomt, V om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576047.3363290778</v>
+        <v>576047</v>
       </c>
       <c r="R2" t="n">
-        <v>6563665.68439744</v>
+        <v>6563666</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,19 +743,9 @@
           <t>2020-06-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-06-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,32 +777,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86361320</v>
+        <v>86361325</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,17 +805,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gofarstorps gamla tomt, V om, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576047.3363290778</v>
+        <v>576047</v>
       </c>
       <c r="R3" t="n">
-        <v>6563665.68439744</v>
+        <v>6563666</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,19 +859,9 @@
           <t>2020-06-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-06-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>86361311</v>
+        <v>86361326</v>
       </c>
       <c r="B4" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,16 +904,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,7 +923,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -968,7 +933,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -977,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576068.0255264083</v>
+        <v>576067</v>
       </c>
       <c r="R4" t="n">
-        <v>6563606.162463542</v>
+        <v>6563676</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,21 +975,11 @@
           <t>2020-06-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-06-07</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1036,7 +991,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Vägkant, mot granskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1054,15 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>86361328</v>
+        <v>86361311</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1039,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1108,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576067.1475311109</v>
+        <v>576068</v>
       </c>
       <c r="R5" t="n">
-        <v>6563675.813011195</v>
+        <v>6563606</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1141,21 +1091,11 @@
           <t>2020-06-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-06-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1167,7 +1107,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Vägkant, mot granskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1185,15 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>86361325</v>
+        <v>86361312</v>
       </c>
       <c r="B6" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,16 +1136,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1220,7 +1155,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1230,7 +1165,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1239,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576047.3363290778</v>
+        <v>576058</v>
       </c>
       <c r="R6" t="n">
-        <v>6563665.68439744</v>
+        <v>6563616</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1272,19 +1207,9 @@
           <t>2020-06-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-06-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1316,15 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>86361312</v>
+        <v>86361313</v>
       </c>
       <c r="B7" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1271,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1370,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576058.0847899221</v>
+        <v>576058</v>
       </c>
       <c r="R7" t="n">
-        <v>6563615.697043261</v>
+        <v>6563626</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1403,19 +1323,9 @@
           <t>2020-06-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-06-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1447,15 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>86361313</v>
+        <v>86361322</v>
       </c>
       <c r="B8" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1387,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1501,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576057.8802630659</v>
+        <v>576047</v>
       </c>
       <c r="R8" t="n">
-        <v>6563625.938317998</v>
+        <v>6563666</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1534,19 +1439,9 @@
           <t>2020-06-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-06-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1578,15 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>86361326</v>
+        <v>86361328</v>
       </c>
       <c r="B9" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,16 +1484,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1613,7 +1503,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1623,7 +1513,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1632,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576067.1475311109</v>
+        <v>576067</v>
       </c>
       <c r="R9" t="n">
-        <v>6563675.813011195</v>
+        <v>6563676</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1665,19 +1555,9 @@
           <t>2020-06-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-06-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 18968-2023 artfynd.xlsx
+++ b/artfynd/A 18968-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86361320</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86361325</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86361326</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86361311</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1238,6 +1263,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86361312</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1354,6 +1384,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86361313</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1470,6 +1505,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86361322</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1586,8 +1626,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86361328</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>